--- a/output/2026-09-06_15_Slovenia_Jugovzhodna_Slovenija_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_15_Slovenia_Jugovzhodna_Slovenija_Utensilerie_e_Macchine_Utensili.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sede confermata via WebSearch (bizi/sito aziendale) a Podbreznik 13, Novo Mesto. Azienda con sede centrale a Vipava e filiali a Ravne na Koroškem, Novo Mesto, Koper. Ampio catalogo di cuscinetti, tecnica lineare, riduttori/motori, cinghie e catene di trasmissione: distributore B2B coerente col settore.</t>
+          <t>Sede confermata via WebSearch (bizi/sito aziendale) a Podbreznik 13, Novo Mesto. Azienda con sede centrale a Vipava e filiali a Ravne na Koroškem, Novo Mesto, Koper. Ampio catalogo di cuscinetti, tecnica lineare, riduttori/motori, cinghie e catene di trasmissione: distributore B2B coerente col settore. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
